--- a/artfynd/A 46984-2021 artfynd.xlsx
+++ b/artfynd/A 46984-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46984-2021 artfynd.xlsx
+++ b/artfynd/A 46984-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86971823</v>
+        <v>86971811</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>371324.8267845802</v>
+        <v>371287</v>
       </c>
       <c r="R2" t="n">
-        <v>7022343.878691505</v>
+        <v>7022334</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2020-07-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,43 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86971838</v>
+        <v>86971823</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>371324.8267845802</v>
+        <v>371325</v>
       </c>
       <c r="R3" t="n">
-        <v>7022343.878691505</v>
+        <v>7022344</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,32 +847,18 @@
           <t>2020-07-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-07-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,6 +874,736 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>86971845</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Timmerkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>371334</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7022343</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86971852</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Timmerkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>371398</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7022338</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>86971810</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Timmerkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>371287</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7022334</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86971838</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Timmerkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>371325</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7022344</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>86971865</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Timmerkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>371399</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7022340</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>86971801</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Timmerkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>371272</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7022323</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnaggångar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>86971877</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Timmerkojan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>371438</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7022363</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-07-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46984-2021 artfynd.xlsx
+++ b/artfynd/A 46984-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971823</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971845</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971852</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971810</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971838</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971865</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971801</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,8 +1649,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86971877</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>